--- a/testData/RegistrationData.xlsx
+++ b/testData/RegistrationData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>First Name</t>
   </si>
@@ -93,6 +93,156 @@
   </si>
   <si>
     <t>2026-07-02T18:06:57.272737100</t>
+  </si>
+  <si>
+    <t>UserFirstName0005</t>
+  </si>
+  <si>
+    <t>UserLastName0005</t>
+  </si>
+  <si>
+    <t>user0005@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0005</t>
+  </si>
+  <si>
+    <t>2026-07-02T18:28:53.778120900</t>
+  </si>
+  <si>
+    <t>UserFirstName0006</t>
+  </si>
+  <si>
+    <t>UserLastName0006</t>
+  </si>
+  <si>
+    <t>user0006@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0006</t>
+  </si>
+  <si>
+    <t>2026-07-02T18:41:42.771031600</t>
+  </si>
+  <si>
+    <t>UserFirstName0007</t>
+  </si>
+  <si>
+    <t>UserLastName0007</t>
+  </si>
+  <si>
+    <t>user0007@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0007</t>
+  </si>
+  <si>
+    <t>2026-07-02T18:53:26.202635100</t>
+  </si>
+  <si>
+    <t>UserFirstName0008</t>
+  </si>
+  <si>
+    <t>UserLastName0008</t>
+  </si>
+  <si>
+    <t>user0008@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0008</t>
+  </si>
+  <si>
+    <t>2026-07-02T18:58:08.056752</t>
+  </si>
+  <si>
+    <t>UserFirstName0009</t>
+  </si>
+  <si>
+    <t>UserLastName0009</t>
+  </si>
+  <si>
+    <t>user0009@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0009</t>
+  </si>
+  <si>
+    <t>2026-07-02T19:01:52.639429800</t>
+  </si>
+  <si>
+    <t>UserFirstName0010</t>
+  </si>
+  <si>
+    <t>UserLastName0010</t>
+  </si>
+  <si>
+    <t>user0010@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0010</t>
+  </si>
+  <si>
+    <t>2026-07-02T19:05:07.033374800</t>
+  </si>
+  <si>
+    <t>UserFirstName0011</t>
+  </si>
+  <si>
+    <t>UserLastName0011</t>
+  </si>
+  <si>
+    <t>user0011@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0011</t>
+  </si>
+  <si>
+    <t>2026-07-02T19:19:28.387292900</t>
+  </si>
+  <si>
+    <t>UserFirstName0012</t>
+  </si>
+  <si>
+    <t>UserLastName0012</t>
+  </si>
+  <si>
+    <t>user0012@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0012</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:36:16.408974500</t>
+  </si>
+  <si>
+    <t>UserFirstName0013</t>
+  </si>
+  <si>
+    <t>UserLastName0013</t>
+  </si>
+  <si>
+    <t>user0013@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0013</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:36:37.600722200</t>
+  </si>
+  <si>
+    <t>UserFirstName0014</t>
+  </si>
+  <si>
+    <t>UserLastName0014</t>
+  </si>
+  <si>
+    <t>user0014@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0014</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:39:22.477315200</t>
   </si>
 </sst>
 </file>
@@ -137,7 +287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -240,6 +390,206 @@
         <v>26</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/testData/RegistrationData.xlsx
+++ b/testData/RegistrationData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="217">
   <si>
     <t>First Name</t>
   </si>
@@ -243,6 +243,426 @@
   </si>
   <si>
     <t>2026-07-02T22:39:22.477315200</t>
+  </si>
+  <si>
+    <t>UserFirstName0015</t>
+  </si>
+  <si>
+    <t>UserLastName0015</t>
+  </si>
+  <si>
+    <t>user0015@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0015</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:45:59.819937500</t>
+  </si>
+  <si>
+    <t>UserFirstName0016</t>
+  </si>
+  <si>
+    <t>UserLastName0016</t>
+  </si>
+  <si>
+    <t>user0016@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0016</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:46:39.811400900</t>
+  </si>
+  <si>
+    <t>UserFirstName0017</t>
+  </si>
+  <si>
+    <t>UserLastName0017</t>
+  </si>
+  <si>
+    <t>user0017@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0017</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:52:44.076361900</t>
+  </si>
+  <si>
+    <t>UserFirstName0018</t>
+  </si>
+  <si>
+    <t>UserLastName0018</t>
+  </si>
+  <si>
+    <t>user0018@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0018</t>
+  </si>
+  <si>
+    <t>2026-07-02T22:53:24.032468900</t>
+  </si>
+  <si>
+    <t>UserFirstName0019</t>
+  </si>
+  <si>
+    <t>UserLastName0019</t>
+  </si>
+  <si>
+    <t>user0019@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0019</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:00:12.634292400</t>
+  </si>
+  <si>
+    <t>UserFirstName0020</t>
+  </si>
+  <si>
+    <t>UserLastName0020</t>
+  </si>
+  <si>
+    <t>user0020@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0020</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:00:52.622216</t>
+  </si>
+  <si>
+    <t>UserFirstName0021</t>
+  </si>
+  <si>
+    <t>UserLastName0021</t>
+  </si>
+  <si>
+    <t>user0021@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0021</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:10:41.275880700</t>
+  </si>
+  <si>
+    <t>UserFirstName0022</t>
+  </si>
+  <si>
+    <t>UserLastName0022</t>
+  </si>
+  <si>
+    <t>user0022@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0022</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:11:24.426924800</t>
+  </si>
+  <si>
+    <t>UserFirstName0023</t>
+  </si>
+  <si>
+    <t>UserLastName0023</t>
+  </si>
+  <si>
+    <t>user0023@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0023</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:22:39.442103900</t>
+  </si>
+  <si>
+    <t>UserFirstName0024</t>
+  </si>
+  <si>
+    <t>UserLastName0024</t>
+  </si>
+  <si>
+    <t>user0024@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0024</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:22:46.796079300</t>
+  </si>
+  <si>
+    <t>UserFirstName0025</t>
+  </si>
+  <si>
+    <t>UserLastName0025</t>
+  </si>
+  <si>
+    <t>user0025@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0025</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:22:53.847536300</t>
+  </si>
+  <si>
+    <t>UserFirstName0026</t>
+  </si>
+  <si>
+    <t>UserLastName0026</t>
+  </si>
+  <si>
+    <t>user0026@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0026</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:23:56.685955400</t>
+  </si>
+  <si>
+    <t>UserFirstName0027</t>
+  </si>
+  <si>
+    <t>UserLastName0027</t>
+  </si>
+  <si>
+    <t>user0027@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0027</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:24:09.409219</t>
+  </si>
+  <si>
+    <t>UserFirstName0028</t>
+  </si>
+  <si>
+    <t>UserLastName0028</t>
+  </si>
+  <si>
+    <t>user0028@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0028</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:24:20.075750600</t>
+  </si>
+  <si>
+    <t>UserFirstName0029</t>
+  </si>
+  <si>
+    <t>UserLastName0029</t>
+  </si>
+  <si>
+    <t>user0029@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0029</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:32:26.694135100</t>
+  </si>
+  <si>
+    <t>UserFirstName0030</t>
+  </si>
+  <si>
+    <t>UserLastName0030</t>
+  </si>
+  <si>
+    <t>user0030@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0030</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:32:34.528573400</t>
+  </si>
+  <si>
+    <t>UserFirstName0031</t>
+  </si>
+  <si>
+    <t>UserLastName0031</t>
+  </si>
+  <si>
+    <t>user0031@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0031</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:32:40.843673800</t>
+  </si>
+  <si>
+    <t>UserFirstName0032</t>
+  </si>
+  <si>
+    <t>UserLastName0032</t>
+  </si>
+  <si>
+    <t>user0032@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0032</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:39:39.527862400</t>
+  </si>
+  <si>
+    <t>UserFirstName0033</t>
+  </si>
+  <si>
+    <t>UserLastName0033</t>
+  </si>
+  <si>
+    <t>user0033@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0033</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:39:46.026988100</t>
+  </si>
+  <si>
+    <t>UserFirstName0034</t>
+  </si>
+  <si>
+    <t>UserLastName0034</t>
+  </si>
+  <si>
+    <t>user0034@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0034</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:39:52.322559600</t>
+  </si>
+  <si>
+    <t>UserFirstName0035</t>
+  </si>
+  <si>
+    <t>UserLastName0035</t>
+  </si>
+  <si>
+    <t>user0035@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0035</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:41:22.731975600</t>
+  </si>
+  <si>
+    <t>UserFirstName0036</t>
+  </si>
+  <si>
+    <t>UserLastName0036</t>
+  </si>
+  <si>
+    <t>user0036@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0036</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:41:28.530567100</t>
+  </si>
+  <si>
+    <t>UserFirstName0037</t>
+  </si>
+  <si>
+    <t>UserLastName0037</t>
+  </si>
+  <si>
+    <t>user0037@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0037</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:41:34.184766100</t>
+  </si>
+  <si>
+    <t>UserFirstName0038</t>
+  </si>
+  <si>
+    <t>UserLastName0038</t>
+  </si>
+  <si>
+    <t>user0038@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0038</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:42:17.031135700</t>
+  </si>
+  <si>
+    <t>UserFirstName0039</t>
+  </si>
+  <si>
+    <t>UserLastName0039</t>
+  </si>
+  <si>
+    <t>user0039@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0039</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:42:31.600946600</t>
+  </si>
+  <si>
+    <t>UserFirstName0040</t>
+  </si>
+  <si>
+    <t>UserLastName0040</t>
+  </si>
+  <si>
+    <t>user0040@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0040</t>
+  </si>
+  <si>
+    <t>2026-07-02T23:42:43.633534700</t>
+  </si>
+  <si>
+    <t>UserFirstName0041</t>
+  </si>
+  <si>
+    <t>UserLastName0041</t>
+  </si>
+  <si>
+    <t>user0041@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0041</t>
+  </si>
+  <si>
+    <t>2026-07-17T19:10:45.361408400</t>
+  </si>
+  <si>
+    <t>UserFirstName0042</t>
+  </si>
+  <si>
+    <t>UserLastName0042</t>
+  </si>
+  <si>
+    <t>user0042@gmail.com</t>
+  </si>
+  <si>
+    <t>TestUser@0042</t>
+  </si>
+  <si>
+    <t>2026-08-01T10:53:47.296158800</t>
   </si>
 </sst>
 </file>
@@ -287,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -590,6 +1010,566 @@
         <v>76</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>193</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
